--- a/trunk/psse_validation/data/ieee9.raw.xlsx
+++ b/trunk/psse_validation/data/ieee9.raw.xlsx
@@ -16,21 +16,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+  <si>
+    <t>names</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>Vm</t>
+  </si>
+  <si>
+    <t>Va(rad)</t>
+  </si>
   <si>
     <t>Va(deg)</t>
   </si>
   <si>
-    <t>Va(rad)</t>
-  </si>
-  <si>
-    <t>Vm</t>
-  </si>
-  <si>
-    <t>names</t>
-  </si>
-  <si>
-    <t>number</t>
+    <t>Vnom</t>
   </si>
   <si>
     <t xml:space="preserve">BUS 1       </t>
@@ -60,10 +63,25 @@
     <t xml:space="preserve">BUS 9       </t>
   </si>
   <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>Q</t>
+    <t>Pf</t>
+  </si>
+  <si>
+    <t>Qf</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>Qt</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>ckt</t>
   </si>
   <si>
     <t>4_5_1</t>
@@ -448,10 +466,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,185 +485,215 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1.03999996185303</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>9.28000899104955</v>
+      <c r="B3" t="s">
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>0.161966711508492</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>1.02500003605304</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="E3">
+        <v>0.161966711508492</v>
       </c>
       <c r="F3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>9.28000899104955</v>
+      </c>
+      <c r="G3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>4.66475549584621</v>
+      <c r="B4" t="s">
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>0.081415342203017</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>1.02499998499187</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
+      <c r="E4">
+        <v>0.081415342203017</v>
       </c>
       <c r="F4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>4.66475549584621</v>
+      </c>
+      <c r="G4">
+        <v>13.8000001907349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>-2.21678682202554</v>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>-0.0386902288591673</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>1.02578874936223</v>
       </c>
-      <c r="E5" t="s">
-        <v>8</v>
+      <c r="E5">
+        <v>-0.0386902288591673</v>
       </c>
       <c r="F5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>-2.21678682202554</v>
+      </c>
+      <c r="G5">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>-3.98880181136975</v>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>-0.069617724817916</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>0.995631187707993</v>
       </c>
-      <c r="E6" t="s">
-        <v>9</v>
+      <c r="E6">
+        <v>-0.069617724817916</v>
       </c>
       <c r="F6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>-3.98880181136975</v>
+      </c>
+      <c r="G6">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>-3.68739569718294</v>
+      <c r="B7" t="s">
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>-0.064357195739714</v>
+        <v>6</v>
       </c>
       <c r="D7">
         <v>1.01265489390055</v>
       </c>
-      <c r="E7" t="s">
-        <v>10</v>
+      <c r="E7">
+        <v>-0.064357195739714</v>
       </c>
       <c r="F7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>-3.68739569718294</v>
+      </c>
+      <c r="G7">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>3.71970534174021</v>
+      <c r="B8" t="s">
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>0.0649211054173875</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>1.02576948712811</v>
       </c>
-      <c r="E8" t="s">
-        <v>11</v>
+      <c r="E8">
+        <v>0.0649211054173875</v>
       </c>
       <c r="F8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>3.71970534174021</v>
+      </c>
+      <c r="G8">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>0.727540517379566</v>
+      <c r="B9" t="s">
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>0.0126979774699365</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>1.01588273237257</v>
       </c>
-      <c r="E9" t="s">
-        <v>12</v>
+      <c r="E9">
+        <v>0.0126979774699365</v>
       </c>
       <c r="F9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>0.727540517379566</v>
+      </c>
+      <c r="G9">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10">
-        <v>1.96672022503595</v>
+      <c r="B10" t="s">
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>0.0343257433924412</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>1.03235308570478</v>
       </c>
-      <c r="E10" t="s">
-        <v>13</v>
+      <c r="E10">
+        <v>0.0343257433924412</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>1.96672022503595</v>
+      </c>
+      <c r="G10">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -655,102 +703,207 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
         <v>40.9373397827148</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>22.8932075500488</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-40.6798252463341</v>
+      </c>
+      <c r="F2">
+        <v>-20.7043340206146</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
         <v>30.7036571502686</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1.02920234203339</v>
       </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-30.5372513085604</v>
+      </c>
+      <c r="F3">
+        <v>-0.128653168678284</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
         <v>-84.320182800293</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>-11.3126354217529</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>86.6201541423798</v>
+      </c>
+      <c r="F4">
+        <v>22.8843650817871</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
         <v>-59.4627571105957</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>-13.4563703536987</v>
       </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>60.8166061639786</v>
+      </c>
+      <c r="F5">
+        <v>19.3577637672424</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
         <v>76.3798828125</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>-0.797358870506287</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>-75.9045991003513</v>
+      </c>
+      <c r="F6">
+        <v>4.82329118251801</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7">
         <v>-24.0954208374023</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>-24.2958488464355</v>
       </c>
-      <c r="D7" t="s">
-        <v>21</v>
+      <c r="E7">
+        <v>24.1834174692631</v>
+      </c>
+      <c r="F7">
+        <v>25.0412320494652</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -760,60 +913,120 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2">
         <v>71.6410064697266</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>27.0451812744141</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>-71.6410064697266</v>
+      </c>
+      <c r="F2">
+        <v>-23.9224066734314</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3">
         <v>163.000015258789</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>6.65347337722778</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>-163.000015258789</v>
+      </c>
+      <c r="F3">
+        <v>9.17833662033081</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4">
         <v>85.0000076293945</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>-10.8599872589111</v>
       </c>
-      <c r="D4" t="s">
-        <v>24</v>
+      <c r="E4">
+        <v>-85.0000076293945</v>
+      </c>
+      <c r="F4">
+        <v>14.9556093215942</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
